--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98451</v>
+        <v>98453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98453</v>
+        <v>98455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98455</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98473</v>
+        <v>98483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98484</v>
+        <v>98489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98489</v>
+        <v>98491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98491</v>
+        <v>98497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98497</v>
+        <v>98509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98509</v>
+        <v>98510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98510</v>
+        <v>98513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24037-2022 artfynd.xlsx
+++ b/artfynd/A 24037-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137146926</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137146881</v>
       </c>
       <c r="B3" t="n">
-        <v>106622</v>
+        <v>106628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137146957</v>
       </c>
       <c r="B4" t="n">
-        <v>98513</v>
+        <v>98517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
